--- a/seed/naidis-raamhange.xlsx
+++ b/seed/naidis-raamhange.xlsx
@@ -164,7 +164,7 @@
     <t>e_post</t>
   </si>
   <si>
-    <t>uhikhind</t>
+    <t>uhikuhind</t>
   </si>
   <si>
     <t>Tehisaru Koolitus OÜ</t>
@@ -182,7 +182,7 @@
     <t>jaan.kask@tehisaru-naidis.ee</t>
   </si>
   <si>
-    <t>1450</t>
+    <t>58</t>
   </si>
   <si>
     <t>AI Akadeemia OÜ</t>
@@ -197,7 +197,7 @@
     <t>liis.magi@ai-akadeemia-naidis.ee</t>
   </si>
   <si>
-    <t>1515</t>
+    <t>60,50</t>
   </si>
   <si>
     <t>Nutikoolitus OÜ</t>
@@ -212,7 +212,7 @@
     <t>kadri.lepik@nutikoolitus-naidis.ee</t>
   </si>
   <si>
-    <t>1580</t>
+    <t>63</t>
   </si>
   <si>
     <t>Targa Töö Koolitus OÜ</t>
@@ -227,7 +227,7 @@
     <t>anu.sepp@targatoo-naidis.ee</t>
   </si>
   <si>
-    <t>1645</t>
+    <t>65,50</t>
   </si>
   <si>
     <t>E-õppe Ekspert OÜ</t>
@@ -242,10 +242,10 @@
     <t>toomas.rand@eoppe-naidis.ee</t>
   </si>
   <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>980</t>
+    <t>68</t>
+  </si>
+  <si>
+    <t>39</t>
   </si>
   <si>
     <t>Digioskus MTÜ</t>
@@ -260,37 +260,37 @@
     <t>peeter.saar@digioskus-naidis.ee</t>
   </si>
   <si>
-    <t>1040</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>1160</t>
-  </si>
-  <si>
-    <t>760</t>
-  </si>
-  <si>
-    <t>820</t>
-  </si>
-  <si>
-    <t>880</t>
-  </si>
-  <si>
-    <t>940</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>4800</t>
-  </si>
-  <si>
-    <t>5300</t>
-  </si>
-  <si>
-    <t>5800</t>
+    <t>41,50</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>46,50</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17,50</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20,50</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>33</t>
   </si>
   <si>
     <t>esindaja</t>
@@ -1047,7 +1047,7 @@
     <col min="3" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">

--- a/seed/naidis-raamhange.xlsx
+++ b/seed/naidis-raamhange.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="133">
   <si>
     <t>väli</t>
   </si>
@@ -389,6 +389,9 @@
     <t>Koht järjestuses; 1 tähendab eesõigust. Kohad on hankeosa piires unikaalsed.</t>
   </si>
   <si>
+    <t>Partneri raamlepingu hind ÜHE OSALEJA KOHTA selles hankeosas, eurodes, komaga (nt 60,50). Koolituse hind rühma täitumisel = max osalejaid × see hind; jaotuse hind max osalejate korral on nende summa. Vana veerunimi „uhikhind“ võetakse samuti vastu.</t>
+  </si>
+  <si>
     <t>Raamlepingu kontaktisiku aadress. Sellele lähevad vooru teated JA sellega saab partner sisse logida — üks aadress esindab ühte ettevõtet.</t>
   </si>
   <si>
@@ -404,7 +407,13 @@
     <t>(kogu leht)</t>
   </si>
   <si>
-    <t>Vabatahtlik. Siia käivad lisainimesed peale raamlepingu kontaktisiku — asendajad ja teised, kes tohivad ettevõtte eest vastata. Kontaktisikut ennast siia lisama ei pea.</t>
+    <t>Vabatahtlik. Siia käivad lisainimesed peale raamlepingu kontaktisiku — asendajad ja teised, kes tohivad ettevõtte eest vastata. Kontaktisikut siia lisama ei pea: tema esindus tuleb järjestusest ja lõpeb kontaktisiku vahetusega. Kes peab pärast kontaktisiku vahetust esindajaks jääma, kirjuta siia samas failis. Alla laaditud failis on siin täpselt need, kes on eraldi nimetatud.</t>
+  </si>
+  <si>
+    <t>(puuduv esindaja)</t>
+  </si>
+  <si>
+    <t>Valik „lõpeta failist puuduvad“ lõpetab ka eraldi nimetatud esindajad, keda sellel lehel ei ole — lehel „Partnerid“ olevate ettevõtete kohta. Raamlepingu kontaktisikuid see ei puuduta.</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1627,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1741,7 +1750,7 @@
         <v>121</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
         <v>124</v>
@@ -1752,21 +1761,43 @@
         <v>121</v>
       </c>
       <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
         <v>125</v>
-      </c>
-      <c r="C12" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" t="s">
         <v>127</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>128</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
         <v>129</v>
+      </c>
+      <c r="C14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/seed/naidis-raamhange.xlsx
+++ b/seed/naidis-raamhange.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="136">
   <si>
     <t>väli</t>
   </si>
@@ -365,6 +365,9 @@
     <t>Hankeosa kood, nt OSA-1. Selle järgi hankeosa leitakse või luuakse.</t>
   </si>
   <si>
+    <t>Hankeosa kirjeldus, nagu partner seda vooru teates ja lehel näeb. Kontrolli, et see vastab raamlepingu sõnastusele — näidisandmete kirjeldused on näidised, mitte raamlepingu tekst.</t>
+  </si>
+  <si>
     <t>(tühi lahter)</t>
   </si>
   <si>
@@ -383,6 +386,12 @@
     <t>Partnerid</t>
   </si>
   <si>
+    <t>(üks rida)</t>
+  </si>
+  <si>
+    <t>Üks rida on ühe ettevõtte koht ühes hankeosas: kolmes hankeosas olev ettevõte on kolmel real, igal oma koht ja hind osaleja kohta. Kontaktisik võib ridadel olla sama — see on üks inimene, kes esindab ettevõtet kõigis nendes hankeosades.</t>
+  </si>
+  <si>
     <t>Hankeosa kood. Uue hankeosa puhul lisa see kõigepealt lehele „Hankeosad“.</t>
   </si>
   <si>
@@ -407,7 +416,7 @@
     <t>(kogu leht)</t>
   </si>
   <si>
-    <t>Vabatahtlik. Siia käivad lisainimesed peale raamlepingu kontaktisiku — asendajad ja teised, kes tohivad ettevõtte eest vastata. Kontaktisikut siia lisama ei pea: tema esindus tuleb järjestusest ja lõpeb kontaktisiku vahetusega. Kes peab pärast kontaktisiku vahetust esindajaks jääma, kirjuta siia samas failis. Alla laaditud failis on siin täpselt need, kes on eraldi nimetatud.</t>
+    <t>Lisaesindajad — hankeosa kontaktisik on esindaja automaatselt. Vabatahtlik leht: siia käivad lisainimesed peale raamlepingu kontaktisiku — asendajad ja teised, kes tohivad ettevõtte eest vastata. Kontaktisikut siia lisama ei pea: tema esindus tuleb järjestusest ja lõpeb kontaktisiku vahetusega. Kes peab pärast kontaktisiku vahetust esindajaks jääma, kirjuta siia samas failis. Alla laaditud failis on siin täpselt need, kes on eraldi nimetatud.</t>
   </si>
   <si>
     <t>(puuduv esindaja)</t>
@@ -1627,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1695,10 +1704,10 @@
         <v>114</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>116</v>
-      </c>
-      <c r="C6" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1706,7 +1715,7 @@
         <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="C7" t="s">
         <v>118</v>
@@ -1717,62 +1726,62 @@
         <v>114</v>
       </c>
       <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>119</v>
-      </c>
-      <c r="C8" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
         <v>121</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
         <v>127</v>
@@ -1780,24 +1789,46 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
         <v>128</v>
-      </c>
-      <c r="B14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>131</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
         <v>132</v>
+      </c>
+      <c r="C16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/seed/naidis-raamhange.xlsx
+++ b/seed/naidis-raamhange.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="139">
   <si>
     <t>väli</t>
   </si>
@@ -80,6 +80,9 @@
     <t>kunnise_markus</t>
   </si>
   <si>
+    <t>max_osalejaid_ruhmas</t>
+  </si>
+  <si>
     <t>OSA-1</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
     <t>koolitused</t>
   </si>
   <si>
+    <t>75</t>
+  </si>
+  <si>
     <t>OSA-2</t>
   </si>
   <si>
@@ -375,6 +381,9 @@
   </si>
   <si>
     <t>Kellaaeg kujul 17:00. Hoia lahter Excelis tekstina, muidu tekib sellest kuupäev.</t>
+  </si>
+  <si>
+    <t>Ühe rühma (töötoa) osalejate ülempiir raamlepingu järgi, nt 75. Tühi = piiri ei ole. Kindla kuupäevaga koolitus, mille max osalejaid on üle piiri, saab impordil hoiatuse; klastri rühm, mis on piirist suurem, lükatakse tagasi.</t>
   </si>
   <si>
     <t>(puuduv hankeosa)</t>
@@ -866,7 +875,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -879,9 +888,10 @@
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
     <col min="10" max="10" width="60" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -912,132 +922,147 @@
       <c r="J1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
         <v>30</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
       </c>
       <c r="J4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1070,416 +1095,416 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1506,33 +1531,33 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -1540,16 +1565,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
         <v>99</v>
-      </c>
-      <c r="D3" t="s">
-        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -1557,16 +1582,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -1574,16 +1599,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -1591,16 +1616,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -1608,16 +1633,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -1636,116 +1661,116 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
         <v>123</v>
@@ -1756,62 +1781,62 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
         <v>132</v>
@@ -1822,13 +1847,24 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>134</v>
       </c>
-      <c r="C17" t="s">
-        <v>135</v>
+      <c r="B18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
